--- a/artfynd/A 40352-2026 artfynd.xlsx
+++ b/artfynd/A 40352-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137318885</v>
       </c>
       <c r="B2" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>137319183</v>
       </c>
       <c r="B3" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>137319391</v>
       </c>
       <c r="B4" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>137318514</v>
       </c>
       <c r="B5" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>137318748</v>
       </c>
       <c r="B6" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>137318800</v>
       </c>
       <c r="B7" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137319905</v>
       </c>
       <c r="B8" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40352-2026 artfynd.xlsx
+++ b/artfynd/A 40352-2026 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>137318748</v>
       </c>
       <c r="B6" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>137318800</v>
       </c>
       <c r="B7" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137319905</v>
       </c>
       <c r="B8" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40352-2026 artfynd.xlsx
+++ b/artfynd/A 40352-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137318885</v>
       </c>
       <c r="B2" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>137319183</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>137319391</v>
       </c>
       <c r="B4" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>137318514</v>
       </c>
       <c r="B5" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>137318748</v>
       </c>
       <c r="B6" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>137318800</v>
       </c>
       <c r="B7" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137319905</v>
       </c>
       <c r="B8" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40352-2026 artfynd.xlsx
+++ b/artfynd/A 40352-2026 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>137318748</v>
       </c>
       <c r="B6" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>137318800</v>
       </c>
       <c r="B7" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137319905</v>
       </c>
       <c r="B8" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40352-2026 artfynd.xlsx
+++ b/artfynd/A 40352-2026 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>137318748</v>
       </c>
       <c r="B6" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>137318800</v>
       </c>
       <c r="B7" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137319905</v>
       </c>
       <c r="B8" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40352-2026 artfynd.xlsx
+++ b/artfynd/A 40352-2026 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>137318748</v>
       </c>
       <c r="B6" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>137318800</v>
       </c>
       <c r="B7" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137319905</v>
       </c>
       <c r="B8" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40352-2026 artfynd.xlsx
+++ b/artfynd/A 40352-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137318885</v>
       </c>
       <c r="B2" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>137319183</v>
       </c>
       <c r="B3" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>137319391</v>
       </c>
       <c r="B4" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>137318514</v>
       </c>
       <c r="B5" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>137318748</v>
       </c>
       <c r="B6" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>137318800</v>
       </c>
       <c r="B7" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137319905</v>
       </c>
       <c r="B8" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
